--- a/data.mn/public/datasets/poverty-rate-national.xlsx
+++ b/data.mn/public/datasets/poverty-rate-national.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -531,4 +532,130 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>он</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ядуурлын_түвшин</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B2" t="n">
+        <v>36.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B3" t="n">
+        <v>35.6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B4" t="n">
+        <v>36.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B5" t="n">
+        <v>35.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B6" t="n">
+        <v>38.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B7" t="n">
+        <v>38.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B8" t="n">
+        <v>33.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B9" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B10" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B11" t="n">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B12" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B13" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>